--- a/Desarrollo/Sistema de Control de Peso (SISCOP)/Analisis/Requisitos/SISCOP-ERS.xlsx
+++ b/Desarrollo/Sistema de Control de Peso (SISCOP)/Analisis/Requisitos/SISCOP-ERS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
   <si>
     <t>LISTA DE REQUISITOS DEL SISTEMA SISCOP</t>
   </si>
@@ -91,7 +91,7 @@
     <t>RQ06</t>
   </si>
   <si>
-    <t>Búsqueda de historia clínica</t>
+    <t>Historia clínica</t>
   </si>
   <si>
     <t>Nutricionista</t>
@@ -115,67 +115,49 @@
     <t>RQ08</t>
   </si>
   <si>
-    <t>Evaluación nutricional inicial</t>
+    <t xml:space="preserve">Evaluación nutricional </t>
   </si>
   <si>
     <t>Registrar evaluación nutricional</t>
   </si>
   <si>
-    <t>El sistema debe permitir registrar los datos de la evaluación del paciente, incluyendo peso, talla y perímetro abdominal, y calcular automáticamente el índice de masa corporal (IMC).</t>
+    <t>El sistema debe permitir registrar los datos de evaluación nutricional del paciente, incluyendo peso, talla y perímetro abdominal, calcular automáticamente el IMC, registrar indicaciones nutricionales y la fecha del próximo control.</t>
   </si>
   <si>
     <t>RQ09</t>
   </si>
   <si>
-    <t>Registrar indicaciones nutricionales</t>
-  </si>
-  <si>
-    <t>El sistema debe permitir registrar las recomendaciones nutricionales del paciente asociadas a una evaluación.</t>
+    <t>Evaluación nutricional</t>
+  </si>
+  <si>
+    <t>Generar grafica de pesos</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir visualizar una gráfica de la evolución del peso del paciente a lo largo del tiempo, a partir de sus registros de evaluación.</t>
   </si>
   <si>
     <t>RQ10</t>
   </si>
   <si>
-    <t>Registrar fecha de próximo control</t>
-  </si>
-  <si>
-    <t>El sistema debe permitir registrar la fecha programada para el siguiente control del paciente, asociada a la evaluación.</t>
+    <t>Editar evaluacion nutricional</t>
+  </si>
+  <si>
+    <t>El sistema debe permitir editar los registros de evaluación del paciente dentro de un plazo máximo de 24 horas desde su registro.</t>
   </si>
   <si>
     <t>RQ11</t>
   </si>
   <si>
-    <t>Seguimiento nutricional</t>
-  </si>
-  <si>
-    <t>Generar grafica de pesos</t>
-  </si>
-  <si>
-    <t>El sistema debe permitir visualizar una gráfica de la evolución del peso del paciente a lo largo del tiempo, a partir de sus registros de evaluación.</t>
+    <t>Generar ficha de evaluacion</t>
+  </si>
+  <si>
+    <t>El sistema debe generar una ficha con los datos registrados en la evaluación nutricional, incluyendo información del paciente, fecha, medidas antropométricas e indicaciones.</t>
   </si>
   <si>
     <t>RQ12</t>
   </si>
   <si>
-    <t>Editar evaluacion nutricional</t>
-  </si>
-  <si>
-    <t>El sistema debe permitir editar los registros de evaluación del paciente dentro de un plazo máximo de 24 horas desde su registro.</t>
-  </si>
-  <si>
-    <t>RQ13</t>
-  </si>
-  <si>
-    <t>Generar ficha de evaluacion</t>
-  </si>
-  <si>
-    <t>El sistema debe generar una ficha con los datos registrados en la evaluación nutricional, incluyendo información del paciente, fecha, medidas antropométricas e indicaciones.</t>
-  </si>
-  <si>
-    <t>RQ14</t>
-  </si>
-  <si>
-    <t>Informe del paciente</t>
+    <t>Informes</t>
   </si>
   <si>
     <t>Generar informe de evolución</t>
@@ -347,7 +329,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:E17" displayName="Tabla_1" name="Tabla_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:E15" displayName="Requisitos" name="Requisitos" id="1">
   <tableColumns count="5">
     <tableColumn name="ID" id="1"/>
     <tableColumn name="Proceso" id="2"/>
@@ -563,7 +545,7 @@
     <col customWidth="1" min="2" max="2" width="23.25"/>
     <col customWidth="1" min="3" max="3" width="19.75"/>
     <col customWidth="1" min="4" max="4" width="37.0"/>
-    <col customWidth="1" min="5" max="5" width="151.75"/>
+    <col customWidth="1" min="5" max="5" width="133.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -803,16 +785,16 @@
         <v>37</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -823,19 +805,19 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -846,10 +828,10 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>27</v>
@@ -860,68 +842,22 @@
       <c r="E14" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
